--- a/PAMF_DIG F2 - monthly2026-07-13.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-13.xlsx
@@ -8152,7 +8152,7 @@
         <v>0.09</v>
       </c>
       <c r="N106" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>

--- a/PAMF_DIG F2 - monthly2026-07-13.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-13.xlsx
@@ -6181,7 +6181,7 @@
         <v>0.09</v>
       </c>
       <c r="N79" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>0.09</v>
       </c>
       <c r="N258" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O258" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>0.09</v>
       </c>
       <c r="N282" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O282" t="inlineStr">
         <is>
